--- a/dashboard/public/starter-pack/05_Certification_Eligibility_Worksheets/FLK_05_WOSB_EDWOSB_Self_Cert.xlsx
+++ b/dashboard/public/starter-pack/05_Certification_Eligibility_Worksheets/FLK_05_WOSB_EDWOSB_Self_Cert.xlsx
@@ -4,20 +4,23 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Instructions" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Business Profile" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="WOSB Eligibility" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="EDWOSB Net Worth" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Document Checklist" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Eligible NAICS" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Summary" state="visible" r:id="rId10"/>
+    <sheet sheetId="1" name="Lists" state="veryHidden" r:id="rId4"/>
+    <sheet sheetId="2" name="Instructions" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Business Profile" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="WOSB Eligibility" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="EDWOSB Net Worth" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Document Checklist" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Eligible NAICS" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Summary" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
+    <definedName name="CitizenStatus">Lists!$A$2:$A$5,'Business Profile'!$C$18</definedName>
+    <definedName name="YesNoMaybe">Lists!$B$2:$B$4</definedName>
+    <definedName name="DocStatus">Lists!$C$2:$C$4,'Document Checklist'!$F$5:$F$32</definedName>
     <definedName name="BusinessName">'Business Profile'!$C$4</definedName>
     <definedName name="PrimaryNAICS">'Business Profile'!$C$8</definedName>
     <definedName name="AvgRevenue">'Business Profile'!$C$13</definedName>
     <definedName name="FemaleOwnerPct">'Business Profile'!$C$17</definedName>
-    <definedName name="CitizenStatus">'Business Profile'!$C$18</definedName>
     <definedName name="CombinedFemalePct">'Business Profile'!$C$22</definedName>
     <definedName name="HighestMalePct">'Business Profile'!$C$23</definedName>
     <definedName name="WOSBCore">'WOSB Eligibility'!$D$5:$D$13</definedName>
@@ -25,13 +28,12 @@
     <definedName name="EDWOSBTests">'WOSB Eligibility'!$D$22:$D$26</definedName>
     <definedName name="WOSBDocs">'WOSB Eligibility'!$D$28:$D$31</definedName>
     <definedName name="WOSBAll">'WOSB Eligibility'!$D$5:$D$31</definedName>
-    <definedName name="DocStatus">'Document Checklist'!$F$5:$F$32</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
@@ -119,14 +121,50 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="319">
+  <si>
+    <t>Citizen Status</t>
+  </si>
+  <si>
+    <t>Y / N / ?</t>
+  </si>
+  <si>
+    <t>Document Status</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Have</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Need</t>
+  </si>
+  <si>
+    <t>Naturalized</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Dual citizen</t>
+  </si>
   <si>
     <t>WOSB / EDWOSB Self-Certification Pack</t>
   </si>
   <si>
-    <t>CHECKBOXES — Google Sheets: cells render as native checkboxes. Excel 365: cells render as boolean dropdowns; right-click &gt; Format Cell &gt; Checkbox to convert. Older Excel: cells show as TRUE/FALSE dropdowns.</t>
-  </si>
-  <si>
     <t>A working assessment for women-owned firms going after federal set-aside contracts</t>
   </si>
   <si>
@@ -358,7 +396,7 @@
     <t>ELIGIBILITY REQUIREMENT</t>
   </si>
   <si>
-    <t>DONE</t>
+    <t>MET? (Y/N/?)</t>
   </si>
   <si>
     <t>RISK</t>
@@ -632,6 +670,9 @@
   </si>
   <si>
     <t>EDWOSB</t>
+  </si>
+  <si>
+    <t>STATUS</t>
   </si>
   <si>
     <t>LOCATION / NOTES</t>
@@ -1047,7 +1088,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;[Red]-&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1057,20 +1098,29 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="18"/>
+      <name val="Helvetica"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF475569"/>
+      <sz val="10"/>
       <name val="Helvetica"/>
     </font>
     <font>
       <b/>
       <color rgb="FF065F46"/>
       <sz val="11"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF475569"/>
-      <sz val="10"/>
       <name val="Helvetica"/>
     </font>
     <font>
@@ -1109,6 +1159,7 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF0F172A"/>
       <sz val="11"/>
       <name val="Helvetica"/>
     </font>
@@ -1127,12 +1178,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0F172A"/>
       <sz val="11"/>
       <name val="Helvetica"/>
     </font>
@@ -1168,17 +1213,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF065F46"/>
+        <fgColor rgb="FFF1F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F5F9"/>
+        <fgColor rgb="FF065F46"/>
       </patternFill>
     </fill>
     <fill>
@@ -1204,6 +1244,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF59E0B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -1264,144 +1309,149 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="18">
     <dxf>
       <font>
         <b/>
@@ -1434,44 +1484,6 @@
           <bgColor rgb="FFFEF3C7"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF065F46"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD1FAE5"/>
-          <bgColor rgb="FFD1FAE5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <i/>
-        <color rgb="FF6B7280"/>
-        <strike/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF065F46"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD1FAE5"/>
-          <bgColor rgb="FFD1FAE5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <i/>
-        <color rgb="FF6B7280"/>
-        <strike/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -1592,44 +1604,6 @@
           <bgColor rgb="FFF1F5F9"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF065F46"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD1FAE5"/>
-          <bgColor rgb="FFD1FAE5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <i/>
-        <color rgb="FF6B7280"/>
-        <strike/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF065F46"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD1FAE5"/>
-          <bgColor rgb="FFD1FAE5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <i/>
-        <color rgb="FF6B7280"/>
-        <strike/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2010,10 +1984,73 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2021,218 +2058,202 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" ht="48" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" ht="64" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" ht="64" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" ht="64" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" ht="64" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" ht="64" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" ht="64" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="27" ht="80" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B32" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B36" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" ht="64" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B37" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
-        <v>3</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" ht="64" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:F4"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Helvetica,Bold"&amp;12CapturePilot &amp;K10B981WOSB / EDWOSB Self-Cert</oddHeader>
     <oddFooter>&amp;LFederal Lead Kit · 05-C&amp;Rcapturepilot.com · Page &amp;P of &amp;N</oddFooter>
@@ -2240,7 +2261,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2257,257 +2278,257 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>33</v>
+      <c r="B3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>35</v>
+      <c r="B4" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>37</v>
+      <c r="B5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>39</v>
+      <c r="B6" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>41</v>
+      <c r="B7" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>43</v>
+      <c r="B8" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>45</v>
+      <c r="B9" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>47</v>
+      <c r="B10" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>49</v>
+      <c r="B11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>51</v>
+      <c r="B12" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>53</v>
+      <c r="B13" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>55</v>
+      <c r="B15" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>57</v>
+      <c r="B16" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>59</v>
+      <c r="B17" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>62</v>
+      <c r="B18" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>64</v>
+      <c r="B19" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>66</v>
+      <c r="B21" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>68</v>
+      <c r="B22" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>70</v>
+      <c r="B23" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>72</v>
+      <c r="B25" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>74</v>
+      <c r="B26" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -2517,11 +2538,11 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose one" error="Pick from the dropdown" sqref="C18">
-      <formula1>"Yes,No,Naturalized,Dual citizen"</formula1>
+      <formula1>CitizenStatus</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Helvetica,Bold"&amp;12CapturePilot &amp;K10B981WOSB / EDWOSB Self-Cert</oddHeader>
     <oddFooter>&amp;LFederal Lead Kit · 05-C&amp;Rcapturepilot.com · Page &amp;P of &amp;N</oddFooter>
@@ -2529,7 +2550,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2546,600 +2567,564 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
+      <c r="A3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="12" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
     </row>
-    <row r="5" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
+    <row r="5" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="13">
         <v>1</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" s="15" t="b">
-        <v>0</v>
+        <v>94</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="13">
         <v>2</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" s="15" t="b">
-        <v>0</v>
+        <v>96</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="13">
         <v>3</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7" s="15" t="b">
-        <v>0</v>
+        <v>97</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="13">
         <v>4</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" s="15" t="b">
-        <v>0</v>
+        <v>98</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="13">
         <v>5</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" s="15" t="b">
-        <v>0</v>
+        <v>99</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="13">
         <v>6</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" s="15" t="b">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="13">
         <v>7</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" s="15" t="b">
-        <v>0</v>
+        <v>101</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="13">
         <v>8</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" s="15" t="b">
-        <v>0</v>
+        <v>102</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="13">
         <v>9</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" s="15" t="b">
-        <v>0</v>
+        <v>103</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="12" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
       <c r="E14" s="12"/>
       <c r="F14" s="12"/>
     </row>
-    <row r="15" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
+    <row r="15" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="13">
         <v>10</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="15" t="b">
-        <v>0</v>
+        <v>105</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="13">
         <v>11</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" s="15" t="b">
-        <v>0</v>
+        <v>106</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="13">
         <v>12</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" s="15" t="b">
-        <v>0</v>
+        <v>108</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="13">
         <v>13</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" s="15" t="b">
-        <v>0</v>
+        <v>109</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="13">
         <v>14</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D19" s="15" t="b">
-        <v>0</v>
+        <v>110</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="13">
         <v>15</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" s="15" t="b">
-        <v>0</v>
+        <v>111</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="12" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
     </row>
-    <row r="22" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="11"/>
+    <row r="22" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="13">
         <v>16</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D22" s="15" t="b">
-        <v>0</v>
+        <v>113</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="13">
         <v>17</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="D23" s="15" t="b">
-        <v>0</v>
+        <v>114</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="13">
         <v>18</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="D24" s="15" t="b">
-        <v>0</v>
+        <v>115</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="13">
         <v>19</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D25" s="15" t="b">
-        <v>0</v>
+        <v>116</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="13">
         <v>20</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D26" s="15" t="b">
-        <v>0</v>
+        <v>117</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="12" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
       <c r="E27" s="12"/>
       <c r="F27" s="12"/>
     </row>
-    <row r="28" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="11"/>
+    <row r="28" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="13">
         <v>21</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D28" s="15" t="b">
-        <v>0</v>
+        <v>119</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="13">
         <v>22</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="D29" s="15" t="b">
-        <v>0</v>
+        <v>120</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="13">
         <v>23</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D30" s="15" t="b">
-        <v>0</v>
+        <v>121</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="13">
         <v>24</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D31" s="15" t="b">
-        <v>0</v>
+        <v>122</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="11"/>
-      <c r="B33" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C33" s="6"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C33" s="7"/>
       <c r="D33" s="19" t="str">
-        <f>COUNTIF(D5:D13,TRUE)&amp;" of 9"</f>
+        <f>COUNTIF(D5:D13,"Y")&amp;" of 9"</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="11"/>
-      <c r="B34" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C34" s="6"/>
+    <row r="34" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C34" s="7"/>
       <c r="D34" s="19" t="str">
-        <f>COUNTIF(D15:D20,TRUE)&amp;" of 6"</f>
+        <f>COUNTIF(D15:D20,"Y")&amp;" of 6"</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="11"/>
-      <c r="B35" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C35" s="6"/>
+    <row r="35" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C35" s="7"/>
       <c r="D35" s="19" t="str">
-        <f>COUNTIF(D22:D26,TRUE)&amp;" of 5"</f>
+        <f>COUNTIF(D22:D26,"Y")&amp;" of 5"</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="11"/>
-      <c r="B36" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C36" s="6"/>
+    <row r="36" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C36" s="7"/>
       <c r="D36" s="19" t="str">
-        <f>COUNTIF(D28:D31,TRUE)&amp;" of 4"</f>
+        <f>COUNTIF(D28:D31,"Y")&amp;" of 4"</f>
         <v/>
       </c>
     </row>
-    <row r="37" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="11"/>
+    <row r="37" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="20" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="21" t="str">
-        <f>COUNTIF(D5:D31,TRUE)&amp;" of 24 met, "&amp;COUNTIF(D5:D31,FALSE)&amp;" open"</f>
+        <f>COUNTIF(D5:D31,"Y")&amp;" of 24 met, "&amp;(COUNTIF(D5:D31,"N")+COUNTIF(D5:D31,"?"))&amp;" open"</f>
         <v/>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="11"/>
+    <row r="39" ht="30" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39" s="22" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C39" s="22"/>
       <c r="D39" s="23" t="str">
-        <f>IF(COUNTIF(D5:D13,TRUE)=9,IF(COUNTIF(D15:D20,TRUE)&gt;=5,"LIKELY ELIGIBLE — Self-certify on SAM.gov","REVIEW CONTROL TESTS — 5+ of 6 should be checked before certifying"),"GAPS IN CORE REQUIREMENTS — Do not self-certify yet")</f>
+        <f>IF(COUNTIF(D5:D13,"Y")=9,IF(COUNTIF(D15:D20,"Y")&gt;=5,"LIKELY ELIGIBLE — Self-certify on SAM.gov","REVIEW CONTROL TESTS — 5+ of 6 should be Y before certifying"),"GAPS IN CORE REQUIREMENTS — Do not self-certify yet")</f>
         <v/>
       </c>
       <c r="E39" s="23"/>
       <c r="F39" s="23"/>
     </row>
-    <row r="40" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="11"/>
+    <row r="40" ht="30" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="22" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="C40" s="22"/>
       <c r="D40" s="23" t="str">
-        <f>IF(COUNTIF(D22:D26,TRUE)=5,IF(COUNTIF(D5:D13,TRUE)=9,"LIKELY ELIGIBLE for EDWOSB","Confirm WOSB core first"),"EDWOSB GAPS — Check Net Worth tab for exact numbers")</f>
+        <f>IF(COUNTIF(D22:D26,"Y")=5,IF(COUNTIF(D5:D13,"Y")=9,"LIKELY ELIGIBLE for EDWOSB","Confirm WOSB core first"),"EDWOSB GAPS — Check Net Worth tab for exact numbers")</f>
         <v/>
       </c>
       <c r="E40" s="23"/>
       <c r="F40" s="23"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1"/>
   <mergeCells count="15">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -3168,45 +3153,25 @@
       <formula>NOT(ISERROR(SEARCH("?",D5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D31">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>D5=TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C5:C31">
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>$D5=TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D31">
-    <cfRule type="expression" dxfId="5" priority="1">
-      <formula>D5=TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C5:C31">
-    <cfRule type="expression" dxfId="6" priority="1">
-      <formula>$D5=TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Pick TRUE or FALSE" error="Use the dropdown to toggle this checkbox." sqref="D10:D13">
-      <formula1>"TRUE,FALSE"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose Y, N, or ?" error="Pick Y (met), N (not met), or ? (unsure)" sqref="D10:D13">
+      <formula1>YesNoMaybe</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Pick TRUE or FALSE" error="Use the dropdown to toggle this checkbox." sqref="D15:D20">
-      <formula1>"TRUE,FALSE"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose Y, N, or ?" error="Pick Y (met), N (not met), or ? (unsure)" sqref="D15:D20">
+      <formula1>YesNoMaybe</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Pick TRUE or FALSE" error="Use the dropdown to toggle this checkbox." sqref="D22:D26">
-      <formula1>"TRUE,FALSE"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose Y, N, or ?" error="Pick Y (met), N (not met), or ? (unsure)" sqref="D22:D26">
+      <formula1>YesNoMaybe</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Pick TRUE or FALSE" error="Use the dropdown to toggle this checkbox." sqref="D28:D31">
-      <formula1>"TRUE,FALSE"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose Y, N, or ?" error="Pick Y (met), N (not met), or ? (unsure)" sqref="D28:D31">
+      <formula1>YesNoMaybe</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Pick TRUE or FALSE" error="Use the dropdown to toggle this checkbox." sqref="D5:D13">
-      <formula1>"TRUE,FALSE"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose Y, N, or ?" error="Pick Y (met), N (not met), or ? (unsure)" sqref="D5:D13">
+      <formula1>YesNoMaybe</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Helvetica,Bold"&amp;12CapturePilot &amp;K10B981WOSB / EDWOSB Self-Cert</oddHeader>
     <oddFooter>&amp;LFederal Lead Kit · 05-C&amp;Rcapturepilot.com · Page &amp;P of &amp;N</oddFooter>
@@ -3214,7 +3179,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3231,44 +3196,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="20" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C3" s="20"/>
       <c r="E3" s="20" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="F3" s="20"/>
     </row>
     <row r="4" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="24" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C4" s="25">
         <v>0</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="F4" s="25">
         <v>0</v>
@@ -3276,13 +3241,13 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C5" s="25">
         <v>0</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="F5" s="25">
         <v>0</v>
@@ -3290,13 +3255,13 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="24" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="C6" s="25">
         <v>0</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="F6" s="25">
         <v>0</v>
@@ -3304,13 +3269,13 @@
     </row>
     <row r="7" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="24" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="C7" s="25">
         <v>0</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="F7" s="27">
         <f>AVERAGE(F4:F6)</f>
@@ -3319,21 +3284,22 @@
     </row>
     <row r="8" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="24" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="C8" s="25">
         <v>0</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="F8" s="28">
+        <v>143</v>
+      </c>
+      <c r="F8" s="28" t="str">
         <f>IF(F7&lt;400000,"PASS","FAIL — over $400K")</f>
+        <v/>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="24" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C9" s="25">
         <v>0</v>
@@ -3341,25 +3307,25 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="24" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="C10" s="25">
         <v>0</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="F10" s="20"/>
     </row>
     <row r="11" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="24" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="C11" s="25">
         <v>0</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="F11" s="29">
         <f>C15</f>
@@ -3368,21 +3334,22 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="24" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="C12" s="25">
         <v>0</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="F12" s="28">
+        <v>150</v>
+      </c>
+      <c r="F12" s="28" t="str">
         <f>IF(F11&lt;6500000,"PASS","FAIL — over $6.5M")</f>
+        <v/>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="24" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="C13" s="25">
         <v>0</v>
@@ -3390,7 +3357,7 @@
     </row>
     <row r="14" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="24" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="C14" s="25">
         <v>0</v>
@@ -3398,34 +3365,35 @@
     </row>
     <row r="15" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="26" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="C15" s="27">
         <f>SUM(C4:C14)</f>
         <v>0</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="F15" s="20"/>
     </row>
     <row r="16" ht="36" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E16" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="F16" s="31">
+        <v>155</v>
+      </c>
+      <c r="F16" s="31" t="str">
         <f>IF(AND(C33&lt;850000,F7&lt;400000,F11&lt;6500000),"PASS all 3 thresholds","FAIL — see thresholds above")</f>
+        <v/>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="20" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C17" s="20"/>
     </row>
     <row r="18" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="24" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C18" s="25">
         <v>0</v>
@@ -3433,7 +3401,7 @@
     </row>
     <row r="19" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="24" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="C19" s="25">
         <v>0</v>
@@ -3441,7 +3409,7 @@
     </row>
     <row r="20" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="24" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="C20" s="25">
         <v>0</v>
@@ -3449,7 +3417,7 @@
     </row>
     <row r="21" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="24" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C21" s="25">
         <v>0</v>
@@ -3457,7 +3425,7 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="24" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="C22" s="25">
         <v>0</v>
@@ -3465,7 +3433,7 @@
     </row>
     <row r="23" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="24" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C23" s="25">
         <v>0</v>
@@ -3473,7 +3441,7 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="24" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C24" s="25">
         <v>0</v>
@@ -3481,7 +3449,7 @@
     </row>
     <row r="25" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="24" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="C25" s="25">
         <v>0</v>
@@ -3489,7 +3457,7 @@
     </row>
     <row r="26" ht="26" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="26" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="C26" s="27">
         <f>SUM(C18:C25)</f>
@@ -3498,13 +3466,13 @@
     </row>
     <row r="28" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="20" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C28" s="20"/>
     </row>
     <row r="29" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="24" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="C29" s="29">
         <f>C15</f>
@@ -3513,7 +3481,7 @@
     </row>
     <row r="30" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="24" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C30" s="29">
         <f>MAX(0,C8-C18)</f>
@@ -3522,7 +3490,7 @@
     </row>
     <row r="31" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="24" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C31" s="29">
         <f>C11</f>
@@ -3531,7 +3499,7 @@
     </row>
     <row r="32" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="24" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="C32" s="29">
         <f>C26</f>
@@ -3540,7 +3508,7 @@
     </row>
     <row r="33" ht="26" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="26" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C33" s="27">
         <f>C15-MAX(0,C8-C18)-C11-C26</f>
@@ -3549,15 +3517,16 @@
     </row>
     <row r="34" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="C34" s="28">
+        <v>172</v>
+      </c>
+      <c r="C34" s="28" t="str">
         <f>IF(C33&lt;850000,"PASS","FAIL — over $850K")</f>
+        <v/>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" s="26" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C36" s="26"/>
       <c r="D36" s="26"/>
@@ -3566,7 +3535,7 @@
     </row>
     <row r="37" ht="32" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="32" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="C37" s="32"/>
       <c r="D37" s="32"/>
@@ -3575,7 +3544,7 @@
     </row>
     <row r="38" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="32" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="C38" s="32"/>
       <c r="D38" s="32"/>
@@ -3584,7 +3553,7 @@
     </row>
     <row r="39" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39" s="32" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="C39" s="32"/>
       <c r="D39" s="32"/>
@@ -3593,7 +3562,7 @@
     </row>
     <row r="40" ht="32" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="32" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="C40" s="32"/>
       <c r="D40" s="32"/>
@@ -3617,39 +3586,39 @@
     <mergeCell ref="B40:F40"/>
   </mergeCells>
   <conditionalFormatting sqref="C34">
-    <cfRule type="containsText" dxfId="7" priority="1">
+    <cfRule type="containsText" dxfId="3" priority="1">
       <formula>NOT(ISERROR(SEARCH("PASS",C34)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="2">
+    <cfRule type="containsText" dxfId="4" priority="2">
       <formula>NOT(ISERROR(SEARCH("FAIL",C34)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="containsText" dxfId="9" priority="1">
+    <cfRule type="containsText" dxfId="5" priority="1">
       <formula>NOT(ISERROR(SEARCH("PASS",F8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="2">
+    <cfRule type="containsText" dxfId="6" priority="2">
       <formula>NOT(ISERROR(SEARCH("FAIL",F8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F12">
-    <cfRule type="containsText" dxfId="11" priority="1">
+    <cfRule type="containsText" dxfId="7" priority="1">
       <formula>NOT(ISERROR(SEARCH("PASS",F12)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="2">
+    <cfRule type="containsText" dxfId="8" priority="2">
       <formula>NOT(ISERROR(SEARCH("FAIL",F12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16">
-    <cfRule type="containsText" dxfId="13" priority="1">
+    <cfRule type="containsText" dxfId="9" priority="1">
       <formula>NOT(ISERROR(SEARCH("PASS",F16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="2">
+    <cfRule type="containsText" dxfId="10" priority="2">
       <formula>NOT(ISERROR(SEARCH("FAIL",F16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Helvetica,Bold"&amp;12CapturePilot &amp;K10B981WOSB / EDWOSB Self-Cert</oddHeader>
     <oddFooter>&amp;LFederal Lead Kit · 05-C&amp;Rcapturepilot.com · Page &amp;P of &amp;N</oddFooter>
@@ -3658,7 +3627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3675,52 +3644,51 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
+      <c r="A3" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>182</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="12" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
@@ -3728,115 +3696,109 @@
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
     </row>
-    <row r="5" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
+    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="13">
         <v>1</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F5" s="15" t="b">
-        <v>0</v>
+        <v>186</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F5" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="13">
         <v>2</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="E6" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F6" s="15" t="b">
-        <v>0</v>
+        <v>188</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F6" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="13">
         <v>3</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="E7" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F7" s="15" t="b">
-        <v>0</v>
+        <v>189</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="13">
         <v>4</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F8" s="15" t="b">
-        <v>0</v>
+        <v>190</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="13">
         <v>5</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F9" s="15" t="b">
-        <v>0</v>
+        <v>191</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="12" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -3844,73 +3806,69 @@
       <c r="F10" s="12"/>
       <c r="G10" s="12"/>
     </row>
-    <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
+    <row r="11" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="13">
         <v>6</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="E11" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F11" s="15" t="b">
-        <v>0</v>
+        <v>193</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F11" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="13">
         <v>7</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="F12" s="15" t="b">
-        <v>0</v>
+        <v>195</v>
+      </c>
+      <c r="F12" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="13">
         <v>8</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F13" s="15" t="b">
-        <v>0</v>
+        <v>196</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F13" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="12" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
@@ -3918,115 +3876,109 @@
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
+    <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="13">
         <v>9</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="D15" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="E15" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F15" s="15" t="b">
-        <v>0</v>
+        <v>198</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="13">
         <v>10</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="D16" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="E16" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="E16" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F16" s="15" t="b">
-        <v>0</v>
+      <c r="F16" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="13">
         <v>11</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="D17" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="E17" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="E17" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F17" s="15" t="b">
-        <v>0</v>
+      <c r="F17" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="13">
         <v>12</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="D18" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F18" s="15" t="b">
-        <v>0</v>
+        <v>202</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F18" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="13">
         <v>13</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="D19" s="34" t="s">
+        <v>203</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="E19" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="E19" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F19" s="15" t="b">
-        <v>0</v>
+      <c r="F19" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="12" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -4034,94 +3986,89 @@
       <c r="F20" s="12"/>
       <c r="G20" s="12"/>
     </row>
-    <row r="21" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="11"/>
+    <row r="21" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="13">
         <v>14</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="D21" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="E21" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F21" s="15" t="b">
-        <v>0</v>
+        <v>205</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F21" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="13">
         <v>15</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D22" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="E22" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F22" s="15" t="b">
-        <v>0</v>
+        <v>206</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E22" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F22" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="13">
         <v>16</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="D23" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="E23" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F23" s="15" t="b">
-        <v>0</v>
+        <v>207</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F23" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="13">
         <v>17</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="D24" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="E24" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F24" s="15" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="D24" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E24" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F24" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="12" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -4129,94 +4076,89 @@
       <c r="F25" s="12"/>
       <c r="G25" s="12"/>
     </row>
-    <row r="26" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="11"/>
+    <row r="26" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="13">
         <v>18</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D26" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="E26" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F26" s="15" t="b">
-        <v>0</v>
+        <v>210</v>
+      </c>
+      <c r="D26" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E26" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F26" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="13">
         <v>19</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="D27" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="E27" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F27" s="15" t="b">
-        <v>0</v>
+        <v>211</v>
+      </c>
+      <c r="D27" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E27" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F27" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="13">
         <v>20</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="D28" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="D28" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="E28" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="E28" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F28" s="15" t="b">
-        <v>0</v>
+      <c r="F28" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="13">
         <v>21</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="D29" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="E29" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F29" s="15" t="b">
-        <v>0</v>
+        <v>213</v>
+      </c>
+      <c r="D29" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E29" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F29" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30" s="12" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
@@ -4224,92 +4166,86 @@
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
     </row>
-    <row r="31" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="11"/>
+    <row r="31" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B31" s="13">
         <v>22</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="F31" s="15" t="b">
-        <v>0</v>
+        <v>214</v>
+      </c>
+      <c r="F31" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B32" s="13">
         <v>23</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="F32" s="15" t="b">
-        <v>0</v>
+        <v>214</v>
+      </c>
+      <c r="F32" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="11"/>
-      <c r="B34" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="35" t="str">
-        <f>COUNTIF(F5:F32,TRUE)&amp;" of 23"</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B34" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="37" t="str">
+        <f>COUNTIF(F5:F32,"Have")&amp;" of 23"</f>
         <v/>
       </c>
-      <c r="G34" s="35"/>
-    </row>
-    <row r="35" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="11"/>
-      <c r="B35" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="35" t="str">
-        <f>COUNTIF(F5:F32,FALSE)&amp;" missing"</f>
+      <c r="G34" s="37"/>
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B35" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="37" t="str">
+        <f>COUNTIF(F5:F32,"Need")&amp;" missing"</f>
         <v/>
       </c>
-      <c r="G35" s="35"/>
-    </row>
-    <row r="36" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="11"/>
+      <c r="G35" s="37"/>
+    </row>
+    <row r="36" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" s="20" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="20"/>
       <c r="E36" s="20"/>
       <c r="F36" s="23" t="str">
-        <f>ROUND(COUNTIF(F5:F32,TRUE)/23*100,0)&amp;"%"</f>
+        <f>ROUND(COUNTIF(F5:F32,"Have")/23*100,0)&amp;"%"</f>
         <v/>
       </c>
       <c r="G36" s="23"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1"/>
   <mergeCells count="14">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -4327,58 +4263,38 @@
     <mergeCell ref="F36:G36"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F32">
-    <cfRule type="containsText" dxfId="15" priority="1">
+    <cfRule type="containsText" dxfId="11" priority="1">
       <formula>NOT(ISERROR(SEARCH("Have",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="2">
+    <cfRule type="containsText" dxfId="12" priority="2">
       <formula>NOT(ISERROR(SEARCH("Need",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="3">
+    <cfRule type="containsText" dxfId="13" priority="3">
       <formula>NOT(ISERROR(SEARCH("N/A",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F32">
-    <cfRule type="expression" dxfId="18" priority="1">
-      <formula>F5=TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C5:C32">
-    <cfRule type="expression" dxfId="19" priority="1">
-      <formula>$F5=TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F32">
-    <cfRule type="expression" dxfId="20" priority="1">
-      <formula>F5=TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C5:C32">
-    <cfRule type="expression" dxfId="21" priority="1">
-      <formula>$F5=TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Pick TRUE or FALSE" error="Use the dropdown to toggle this checkbox." sqref="F11:F13">
-      <formula1>"TRUE,FALSE"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose status" error="Pick Have, Need, or N/A" sqref="F11:F13">
+      <formula1>DocStatus</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Pick TRUE or FALSE" error="Use the dropdown to toggle this checkbox." sqref="F15:F19">
-      <formula1>"TRUE,FALSE"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose status" error="Pick Have, Need, or N/A" sqref="F15:F19">
+      <formula1>DocStatus</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Pick TRUE or FALSE" error="Use the dropdown to toggle this checkbox." sqref="F21:F24">
-      <formula1>"TRUE,FALSE"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose status" error="Pick Have, Need, or N/A" sqref="F21:F24">
+      <formula1>DocStatus</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Pick TRUE or FALSE" error="Use the dropdown to toggle this checkbox." sqref="F26:F29">
-      <formula1>"TRUE,FALSE"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose status" error="Pick Have, Need, or N/A" sqref="F26:F29">
+      <formula1>DocStatus</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Pick TRUE or FALSE" error="Use the dropdown to toggle this checkbox." sqref="F31:F32">
-      <formula1>"TRUE,FALSE"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose status" error="Pick Have, Need, or N/A" sqref="F31:F32">
+      <formula1>DocStatus</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Pick TRUE or FALSE" error="Use the dropdown to toggle this checkbox." sqref="F5:F9">
-      <formula1>"TRUE,FALSE"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose status" error="Pick Have, Need, or N/A" sqref="F5:F9">
+      <formula1>DocStatus</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Helvetica,Bold"&amp;12CapturePilot &amp;K10B981WOSB / EDWOSB Self-Cert</oddHeader>
     <oddFooter>&amp;LFederal Lead Kit · 05-C&amp;Rcapturepilot.com · Page &amp;P of &amp;N</oddFooter>
@@ -4386,7 +4302,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4402,243 +4318,243 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="36" t="s">
-        <v>209</v>
-      </c>
-      <c r="C3" s="36" t="s">
-        <v>210</v>
-      </c>
-      <c r="D3" s="36" t="s">
-        <v>211</v>
+      <c r="A3" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>222</v>
+      </c>
+      <c r="C3" s="38" t="s">
+        <v>223</v>
+      </c>
+      <c r="D3" s="38" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="C4" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="D4" s="39" t="s">
-        <v>214</v>
+      <c r="B4" s="39" t="s">
+        <v>225</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>226</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="D5" s="39" t="s">
-        <v>217</v>
+      <c r="B5" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>229</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="37" t="s">
-        <v>218</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="D6" s="39" t="s">
-        <v>220</v>
+      <c r="B6" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="37" t="s">
-        <v>221</v>
-      </c>
-      <c r="C7" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="D7" s="39" t="s">
-        <v>223</v>
+      <c r="B7" s="39" t="s">
+        <v>234</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>235</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="37" t="s">
-        <v>224</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="D8" s="39" t="s">
-        <v>226</v>
+      <c r="B8" s="39" t="s">
+        <v>237</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="37" t="s">
-        <v>227</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>228</v>
-      </c>
-      <c r="D9" s="39" t="s">
-        <v>229</v>
+      <c r="B9" s="39" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="37" t="s">
-        <v>230</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>231</v>
-      </c>
-      <c r="D10" s="39" t="s">
-        <v>232</v>
+      <c r="B10" s="39" t="s">
+        <v>243</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="37" t="s">
-        <v>233</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>235</v>
+      <c r="B11" s="39" t="s">
+        <v>246</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>247</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="D12" s="39" t="s">
-        <v>238</v>
+      <c r="B12" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>250</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="37" t="s">
-        <v>239</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>240</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>241</v>
+      <c r="B13" s="39" t="s">
+        <v>252</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>253</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="37" t="s">
-        <v>242</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>243</v>
-      </c>
-      <c r="D14" s="39" t="s">
-        <v>244</v>
+      <c r="B14" s="39" t="s">
+        <v>255</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>256</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="37" t="s">
-        <v>245</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>246</v>
-      </c>
-      <c r="D15" s="39" t="s">
-        <v>247</v>
+      <c r="B15" s="39" t="s">
+        <v>258</v>
+      </c>
+      <c r="C15" s="40" t="s">
+        <v>259</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="37" t="s">
-        <v>248</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>249</v>
-      </c>
-      <c r="D16" s="39" t="s">
-        <v>250</v>
+      <c r="B16" s="39" t="s">
+        <v>261</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>262</v>
+      </c>
+      <c r="D16" s="41" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="37" t="s">
-        <v>251</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>252</v>
-      </c>
-      <c r="D17" s="39" t="s">
-        <v>253</v>
+      <c r="B17" s="39" t="s">
+        <v>264</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="D17" s="41" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>255</v>
-      </c>
-      <c r="D18" s="39" t="s">
-        <v>256</v>
+      <c r="B18" s="39" t="s">
+        <v>267</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>268</v>
+      </c>
+      <c r="D18" s="41" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="37" t="s">
-        <v>257</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="D19" s="39" t="s">
-        <v>259</v>
+      <c r="B19" s="39" t="s">
+        <v>270</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>271</v>
+      </c>
+      <c r="D19" s="41" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>261</v>
-      </c>
-      <c r="D20" s="39" t="s">
-        <v>262</v>
+      <c r="B20" s="39" t="s">
+        <v>273</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>274</v>
+      </c>
+      <c r="D20" s="41" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="37" t="s">
-        <v>263</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>264</v>
-      </c>
-      <c r="D21" s="39" t="s">
-        <v>265</v>
+      <c r="B21" s="39" t="s">
+        <v>276</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>277</v>
+      </c>
+      <c r="D21" s="41" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="23" ht="80" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="40" t="s">
-        <v>266</v>
-      </c>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
+      <c r="B23" s="42" t="s">
+        <v>279</v>
+      </c>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4647,7 +4563,7 @@
     <mergeCell ref="B23:D23"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Helvetica,Bold"&amp;12CapturePilot &amp;K10B981WOSB / EDWOSB Self-Cert</oddHeader>
     <oddFooter>&amp;LFederal Lead Kit · 05-C&amp;Rcapturepilot.com · Page &amp;P of &amp;N</oddFooter>
@@ -4655,7 +4571,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4671,254 +4587,267 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
+      <c r="B3" s="43" t="s">
+        <v>282</v>
+      </c>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="C4" s="21">
+      <c r="B4" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="C4" s="21" t="str">
         <f>IF(BusinessName="","(enter in Business Profile)",BusinessName)</f>
-      </c>
-      <c r="D4" s="42" t="s">
-        <v>271</v>
+        <v/>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="C5" s="21">
+      <c r="B5" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="C5" s="21" t="str">
         <f>IF(PrimaryNAICS="","(enter in Business Profile)",PrimaryNAICS)</f>
-      </c>
-      <c r="D5" s="42" t="s">
-        <v>273</v>
+        <v/>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="C6" s="21">
+      <c r="B6" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="C6" s="21" t="str">
         <f>IF(FemaleOwnerPct="","(enter)",FemaleOwnerPct&amp;"%")</f>
-      </c>
-      <c r="D6" s="42" t="s">
-        <v>275</v>
+        <v/>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="41" t="s">
-        <v>276</v>
-      </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
+      <c r="B8" s="43" t="s">
+        <v>289</v>
+      </c>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
     </row>
     <row r="9" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C9" s="21">
+      <c r="B9" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="C9" s="21" t="str">
         <f>COUNTIF(WOSBCore,"Y")&amp;" / 9"</f>
-      </c>
-      <c r="D9" s="42" t="s">
-        <v>278</v>
+        <v/>
+      </c>
+      <c r="D9" s="44" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="C10" s="21">
+      <c r="B10" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C10" s="21" t="str">
         <f>COUNTIF(WOSBControl,"Y")&amp;" / 6"</f>
-      </c>
-      <c r="D10" s="42" t="s">
-        <v>280</v>
+        <v/>
+      </c>
+      <c r="D10" s="44" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="C11" s="21">
+      <c r="B11" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C11" s="21" t="str">
         <f>COUNTIF(EDWOSBTests,"Y")&amp;" / 5"</f>
-      </c>
-      <c r="D11" s="42" t="s">
-        <v>282</v>
+        <v/>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="C12" s="21">
+      <c r="B12" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="C12" s="21" t="str">
         <f>COUNTIF(WOSBDocs,"Y")&amp;" / 4"</f>
-      </c>
-      <c r="D12" s="42" t="s">
-        <v>284</v>
+        <v/>
+      </c>
+      <c r="D12" s="44" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="C13" s="21">
+      <c r="B13" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="C13" s="21" t="str">
         <f>COUNTIF(DocStatus,"Have")&amp;" of "&amp;COUNTA(DocStatus)</f>
-      </c>
-      <c r="D13" s="42" t="s">
-        <v>286</v>
+        <v/>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="41" t="s">
-        <v>287</v>
-      </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
+      <c r="B15" s="43" t="s">
+        <v>300</v>
+      </c>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
     </row>
     <row r="16" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="C16" s="21">
+      <c r="B16" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="C16" s="21" t="str">
         <f>IF('EDWOSB Net Worth'!C33&lt;850000,"PASS  ($"&amp;TEXT('EDWOSB Net Worth'!C33,"#,##0")&amp;" / $850K)","FAIL  ($"&amp;TEXT('EDWOSB Net Worth'!C33,"#,##0")&amp;" / $850K)")</f>
-      </c>
-      <c r="D16" s="42" t="s">
-        <v>289</v>
+        <v/>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="C17" s="21">
+      <c r="B17" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="C17" s="21" t="str">
         <f>IF('EDWOSB Net Worth'!F7&lt;400000,"PASS  ($"&amp;TEXT('EDWOSB Net Worth'!F7,"#,##0")&amp;" avg)","FAIL  ($"&amp;TEXT('EDWOSB Net Worth'!F7,"#,##0")&amp;" avg)")</f>
-      </c>
-      <c r="D17" s="42" t="s">
-        <v>291</v>
+        <v/>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="C18" s="21">
+      <c r="B18" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="C18" s="21" t="str">
         <f>IF('EDWOSB Net Worth'!C15&lt;6500000,"PASS  ($"&amp;TEXT('EDWOSB Net Worth'!C15,"#,##0")&amp;" / $6.5M)","FAIL  ($"&amp;TEXT('EDWOSB Net Worth'!C15,"#,##0")&amp;" / $6.5M)")</f>
-      </c>
-      <c r="D18" s="42" t="s">
-        <v>293</v>
+        <v/>
+      </c>
+      <c r="D18" s="44" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="41" t="s">
-        <v>294</v>
-      </c>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
+      <c r="B20" s="43" t="s">
+        <v>307</v>
+      </c>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
     </row>
     <row r="21" ht="40" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="43" t="s">
-        <v>295</v>
-      </c>
-      <c r="C21" s="31">
+      <c r="B21" s="45" t="s">
+        <v>308</v>
+      </c>
+      <c r="C21" s="31" t="str">
         <f>IF(AND(COUNTIF(WOSBCore,"Y")=9,COUNTIF(WOSBControl,"Y")&gt;=5),"READY — Go update SAM.gov reps &amp; certs","NOT READY — Resolve gaps in WOSB Eligibility tab first")</f>
+        <v/>
       </c>
       <c r="D21" s="31"/>
     </row>
     <row r="22" ht="40" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="43" t="s">
-        <v>296</v>
-      </c>
-      <c r="C22" s="31">
+      <c r="B22" s="45" t="s">
+        <v>309</v>
+      </c>
+      <c r="C22" s="31" t="str">
         <f>IF(AND(COUNTIF(WOSBCore,"Y")=9,COUNTIF(EDWOSBTests,"Y")=5,'EDWOSB Net Worth'!C33&lt;850000,'EDWOSB Net Worth'!F7&lt;400000,'EDWOSB Net Worth'!C15&lt;6500000),"READY — Self-certify EDWOSB on SAM.gov","NOT READY — Check Net Worth tab + EDWOSB section above")</f>
+        <v/>
       </c>
       <c r="D22" s="31"/>
     </row>
     <row r="24" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="26" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="C24" s="26"/>
       <c r="D24" s="26"/>
     </row>
     <row r="25" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="44" t="s">
-        <v>298</v>
-      </c>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
+      <c r="B25" s="46" t="s">
+        <v>311</v>
+      </c>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
     </row>
     <row r="26" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="44" t="s">
-        <v>299</v>
-      </c>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
+      <c r="B26" s="46" t="s">
+        <v>312</v>
+      </c>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
     </row>
     <row r="27" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B27" s="44" t="s">
-        <v>300</v>
-      </c>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
+      <c r="B27" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
     </row>
     <row r="28" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B28" s="44" t="s">
-        <v>301</v>
-      </c>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
+      <c r="B28" s="46" t="s">
+        <v>314</v>
+      </c>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
     </row>
     <row r="29" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B29" s="44" t="s">
-        <v>302</v>
-      </c>
-      <c r="C29" s="44"/>
-      <c r="D29" s="44"/>
+      <c r="B29" s="46" t="s">
+        <v>315</v>
+      </c>
+      <c r="C29" s="46"/>
+      <c r="D29" s="46"/>
     </row>
     <row r="30" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="44" t="s">
-        <v>303</v>
-      </c>
-      <c r="C30" s="44"/>
-      <c r="D30" s="44"/>
+      <c r="B30" s="46" t="s">
+        <v>316</v>
+      </c>
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
     </row>
     <row r="31" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B31" s="44" t="s">
-        <v>304</v>
-      </c>
-      <c r="C31" s="44"/>
-      <c r="D31" s="44"/>
+      <c r="B31" s="46" t="s">
+        <v>317</v>
+      </c>
+      <c r="C31" s="46"/>
+      <c r="D31" s="46"/>
     </row>
     <row r="32" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="44" t="s">
-        <v>305</v>
-      </c>
-      <c r="C32" s="44"/>
-      <c r="D32" s="44"/>
+      <c r="B32" s="46" t="s">
+        <v>318</v>
+      </c>
+      <c r="C32" s="46"/>
+      <c r="D32" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -4941,21 +4870,21 @@
     <mergeCell ref="B32:D32"/>
   </mergeCells>
   <conditionalFormatting sqref="C17:D33">
-    <cfRule type="containsText" dxfId="22" priority="1">
+    <cfRule type="containsText" dxfId="14" priority="1">
       <formula>NOT(ISERROR(SEARCH("NOT READY",C17)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="2">
+    <cfRule type="containsText" dxfId="15" priority="2">
       <formula>NOT(ISERROR(SEARCH("READY",C17)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="3">
+    <cfRule type="containsText" dxfId="16" priority="3">
       <formula>NOT(ISERROR(SEARCH("FAIL",C17)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="4">
+    <cfRule type="containsText" dxfId="17" priority="4">
       <formula>NOT(ISERROR(SEARCH("PASS",C17)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Helvetica,Bold"&amp;12CapturePilot &amp;K10B981WOSB / EDWOSB Self-Cert</oddHeader>
     <oddFooter>&amp;LFederal Lead Kit · 05-C&amp;Rcapturepilot.com · Page &amp;P of &amp;N</oddFooter>
